--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>sobia9991@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1477-7943</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://www.instagram.com/ptzoa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1258</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="n">
-        <v>1384</v>
+        <v>308</v>
       </c>
       <c r="R2" t="n">
-        <v>2642</v>
+        <v>476</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1131791300</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1131791300</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sobia9991@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1477-7943</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ptzoa</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +695,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>168</v>
+        <v>4442</v>
       </c>
       <c r="Q3" t="n">
-        <v>308</v>
+        <v>1073</v>
       </c>
       <c r="R3" t="n">
-        <v>476</v>
+        <v>5515</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1131791300</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131791300</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>사이언스짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>challenger2017@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1390-2467</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 유성구 온천로 60 유성사이언스타운 2층 사이언스짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>https://blog.naver.com/challenger2017</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
+          <t>https://talk.naver.com/ct/wq5sozu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4442</v>
+        <v>320</v>
       </c>
       <c r="Q4" t="n">
-        <v>1074</v>
+        <v>745</v>
       </c>
       <c r="R4" t="n">
-        <v>5516</v>
+        <v>1065</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>34480701</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/34480701</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>사이언스짐</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>challenger2017@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1390-2467</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 유성구 온천로 60 유성사이언스타운 2층 사이언스짐</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/challenger2017</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wq5sozu</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>320</v>
+        <v>1258</v>
       </c>
       <c r="Q5" t="n">
-        <v>745</v>
+        <v>1384</v>
       </c>
       <c r="R5" t="n">
-        <v>1065</v>
+        <v>2642</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>34480701</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34480701</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1016,10 +1016,10 @@
         <v>377</v>
       </c>
       <c r="Q6" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R6" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1241,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포레스트 필라테스 괴정점</t>
+          <t>다듬체</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>forestgigu@naver.com</t>
+          <t>hamoneji@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-9684</t>
+          <t>042-482-6009</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
+          <t>대전 서구 대덕대로 179 10층 1001호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestpila__gj</t>
+          <t>https://www.instagram.com/dadeumche.pt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlha8ui</t>
+          <t>https://talk.naver.com/ct/wchi4s</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>629</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>845</v>
+        <v>624</v>
       </c>
       <c r="R9" t="n">
-        <v>1474</v>
+        <v>640</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1359870527</t>
+          <t>21661051</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359870527</t>
+          <t>https://m.place.naver.com/place/21661051</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>포레스트 필라테스 괴정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>forestgigu@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1428-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://www.instagram.com/forestpila__gj</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/wlha8ui</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>630</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>847</v>
       </c>
       <c r="R10" t="n">
-        <v>167</v>
+        <v>1477</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1359870527</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1359870527</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1435,20 +1435,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>바벨피트니스 서대전네거리역점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>barbell10@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1411-4881</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>대전 중구 중앙로 8 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/barbell10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,20 +1474,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyzclgu</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,93 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>2046682649</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/2046682649</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6406413</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/6406413</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sobia9991@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1477-7943</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ptzoa</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4kl17</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>168</v>
+        <v>1255</v>
       </c>
       <c r="Q2" t="n">
-        <v>308</v>
+        <v>1395</v>
       </c>
       <c r="R2" t="n">
-        <v>476</v>
+        <v>2650</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1131791300</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131791300</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>건축자재,용품</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>순전가설산업</t>
+          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>safesoon@naver.com</t>
+          <t>sobia9991@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1442-2338</t>
+          <t>0507-1477-7943</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 대덕구 대전로 1011</t>
+          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://2331.co.kr</t>
+          <t>https://www.instagram.com/ptzoa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="Q3" t="n">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="R3" t="n">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16022221</t>
+          <t>1131791300</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16022221</t>
+          <t>https://m.place.naver.com/place/1131791300</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1331,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1255</v>
+        <v>3509</v>
       </c>
       <c r="Q10" t="n">
-        <v>1395</v>
+        <v>360</v>
       </c>
       <c r="R10" t="n">
-        <v>2650</v>
+        <v>3869</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>168</v>
       </c>
       <c r="Q3" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         <v>967</v>
       </c>
       <c r="Q5" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R5" t="n">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
         <v>727</v>
       </c>
       <c r="Q6" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="R6" t="n">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q7" t="n">
         <v>204</v>
       </c>
       <c r="R7" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1335,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3509</v>
+        <v>107</v>
       </c>
       <c r="Q10" t="n">
-        <v>360</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>3869</v>
+        <v>169</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>16151158</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/16151158</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>바벨피트니스 서대전네거리역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>barbell10@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1411-4881</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 중구 중앙로 8 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://blog.naver.com/barbell10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/wyzclgu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>341</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="R11" t="n">
-        <v>169</v>
+        <v>437</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1514,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>2046682649</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/2046682649</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>미라클핏PT오류점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bluepontos1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1444-0534</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 중구 오류로 28 신촌빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/r.sook7502?igshid=NDk5N2NlZjQ=</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41nmr</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>609</v>
+      </c>
+      <c r="R12" t="n">
+        <v>726</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>305286401</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/305286401</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>sobia9991@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1477-7943</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://www.instagram.com/ptzoa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1255</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="n">
-        <v>1395</v>
+        <v>309</v>
       </c>
       <c r="R2" t="n">
-        <v>2650</v>
+        <v>477</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1131791300</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1131791300</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축자재,용품</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
+          <t>순전가설산업</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sobia9991@naver.com</t>
+          <t>safesoon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1477-7943</t>
+          <t>0507-1442-2338</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
+          <t>대전 대덕구 대전로 1011</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ptzoa</t>
+          <t>http://2331.co.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="n">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="R3" t="n">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1131791300</t>
+          <t>16022221</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131791300</t>
+          <t>https://m.place.naver.com/place/16022221</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4468</v>
+        <v>4469</v>
       </c>
       <c r="Q4" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="R4" t="n">
-        <v>5546</v>
+        <v>5548</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q7" t="n">
         <v>204</v>
       </c>
       <c r="R7" t="n">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1242,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포레스트 필라테스 괴정점</t>
+          <t>주 필라테스&amp;요가 관평점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>forestgigu@naver.com</t>
+          <t>jugwpy7755@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-9684</t>
+          <t>0507-1399-7758</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
+          <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestpila__gj</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlha8ui</t>
+          <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>634</v>
+        <v>116</v>
       </c>
       <c r="Q9" t="n">
-        <v>856</v>
+        <v>339</v>
       </c>
       <c r="R9" t="n">
-        <v>1490</v>
+        <v>455</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1359870527</t>
+          <t>1618277867</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359870527</t>
+          <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>포레스트 필라테스 괴정��</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>forestgigu@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1428-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://www.instagram.com/forestpila__gj</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/wlha8ui</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>634</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>856</v>
       </c>
       <c r="R10" t="n">
-        <v>169</v>
+        <v>1490</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1359870527</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1359870527</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>sobia9991@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1477-7943</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ptzoa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1255</v>
+        <v>168</v>
       </c>
       <c r="Q2" t="n">
-        <v>1395</v>
+        <v>309</v>
       </c>
       <c r="R2" t="n">
-        <v>2650</v>
+        <v>477</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1131791300</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1131791300</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
+          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sobia9991@naver.com</t>
+          <t>barbellf07@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1477-7943</t>
+          <t>0507-1466-6683</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
+          <t>대전 중구 중앙로164번길 22-12 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/barbellf07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,20 +690,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uuci</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="Q3" t="n">
-        <v>309</v>
+        <v>199</v>
       </c>
       <c r="R3" t="n">
-        <v>477</v>
+        <v>1353</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1131791300</t>
+          <t>1141342986</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131791300</t>
+          <t>https://m.place.naver.com/place/1141342986</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Q6" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="R6" t="n">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/weonfitness1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/barbell_SIX6th/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1433,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>3511</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>360</v>
       </c>
       <c r="R11" t="n">
-        <v>169</v>
+        <v>3871</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1514,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>바벨피트니스 서대전네거리역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>barbell10@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1411-4881</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 중구 중앙로 8 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbell10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyzclgu</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>342</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>96</v>
+      </c>
+      <c r="R12" t="n">
+        <v>438</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2046682649</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046682649</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
+          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sobia9991@naver.com</t>
+          <t>barbellf07@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1477-7943</t>
+          <t>0507-1466-6683</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
+          <t>대전 중구 중앙로164번길 22-12 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ptzoa</t>
+          <t>https://blog.naver.com/barbellf07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uuci</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="Q2" t="n">
-        <v>309</v>
+        <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>477</v>
+        <v>1353</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1131791300</t>
+          <t>1141342986</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131791300</t>
+          <t>https://m.place.naver.com/place/1141342986</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>barbellf07@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1466-6683</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 중구 중앙로164번길 22-12 3층</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbellf07</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uuci</t>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1154</v>
+        <v>4469</v>
       </c>
       <c r="Q3" t="n">
-        <v>199</v>
+        <v>1080</v>
       </c>
       <c r="R3" t="n">
-        <v>1353</v>
+        <v>5549</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1141342986</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141342986</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>트레인휘트니스 유성점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>train_fitness1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1343-6142</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 유성구 온천서로 2 케이티온 유성타워 2층 201호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>https://blog.naver.com/train_fitness1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,14 +802,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4470</v>
+        <v>967</v>
       </c>
       <c r="Q4" t="n">
-        <v>1079</v>
+        <v>543</v>
       </c>
       <c r="R4" t="n">
-        <v>5549</v>
+        <v>1510</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>1881350370</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/1881350370</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>트레인휘트니스 유성점</t>
+          <t>원알엠 PT &amp; 재활트레이닝 관저점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>train_fitness1@naver.com</t>
+          <t>1rmgym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-6142</t>
+          <t>0507-1311-1989</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 유성구 온천서로 2 케이티온 유성타워 2층 201호</t>
+          <t>대전 서구 관저로 25 초이스프라자 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/train_fitness1</t>
+          <t>https://blog.naver.com/1rmgym/224197109345</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44jzd</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>967</v>
+        <v>728</v>
       </c>
       <c r="Q5" t="n">
-        <v>543</v>
+        <v>638</v>
       </c>
       <c r="R5" t="n">
-        <v>1510</v>
+        <v>1366</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1881350370</t>
+          <t>1117865840</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881350370</t>
+          <t>https://m.place.naver.com/place/1117865840</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -948,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>원알엠 PT &amp; 재활트레이닝 관저점</t>
+          <t>위온 휘트니스 월평점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1rmgym@naver.com</t>
+          <t>weonfitness1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1311-1989</t>
+          <t>042-488-1101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 서구 관저로 25 초이스프라자 5층</t>
+          <t>대전 서구 청사로 65 황실코아 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1rmgym/224197109345</t>
+          <t>https://blog.naver.com/weonfitness1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44jzd</t>
+          <t>https://talk.naver.com/ct/wbsx2z0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>728</v>
+        <v>395</v>
       </c>
       <c r="Q6" t="n">
-        <v>637</v>
+        <v>205</v>
       </c>
       <c r="R6" t="n">
-        <v>1365</v>
+        <v>600</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1117865840</t>
+          <t>2031828897</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117865840</t>
+          <t>https://m.place.naver.com/place/2031828897</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>위온 휘트니스 월평점</t>
+          <t>바벨피트니스 둔산탄방점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weonfitness1@naver.com</t>
+          <t>fit34@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>042-488-1101</t>
+          <t>0507-1334-1836</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 서구 청사로 65 황실코아 B1층</t>
+          <t>대전 서구 둔산로 220 7층 701,702,703호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/weonfitness1</t>
+          <t>https://www.instagram.com/barbell_SIX6th/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbsx2z0</t>
+          <t>https://talk.naver.com/ct/w5ychq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>395</v>
+        <v>640</v>
       </c>
       <c r="Q7" t="n">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="R7" t="n">
-        <v>600</v>
+        <v>769</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2031828897</t>
+          <t>1274875802</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031828897</t>
+          <t>https://m.place.naver.com/place/1274875802</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바벨피트니스 둔산탄방점</t>
+          <t>주 필라테스&amp;요가 관평점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fit34@naver.com</t>
+          <t>jugwpy7755@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1334-1836</t>
+          <t>0507-1399-7758</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 220 7층 701,702,703호</t>
+          <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbell_SIX6th/</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ychq</t>
+          <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>640</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="n">
-        <v>129</v>
+        <v>339</v>
       </c>
       <c r="R8" t="n">
-        <v>769</v>
+        <v>455</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1274875802</t>
+          <t>1618277867</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274875802</t>
+          <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>포레스트 필라테스 괴정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>forestgigu@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>0507-1428-9684</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
+          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jupilates11</t>
+          <t>https://www.instagram.com/forestpila__gj</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
+          <t>https://talk.naver.com/ct/wlha8ui</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>634</v>
       </c>
       <c r="Q9" t="n">
-        <v>339</v>
+        <v>856</v>
       </c>
       <c r="R9" t="n">
-        <v>455</v>
+        <v>1490</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1618277867</t>
+          <t>1359870527</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
+          <t>https://m.place.naver.com/place/1359870527</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>포레스트 필라테스 괴정점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>forestgigu@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1428-9684</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestpila__gj</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlha8ui</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>634</v>
+        <v>3511</v>
       </c>
       <c r="Q10" t="n">
-        <v>856</v>
+        <v>360</v>
       </c>
       <c r="R10" t="n">
-        <v>1490</v>
+        <v>3871</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1359870527</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359870527</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3511</v>
+        <v>1256</v>
       </c>
       <c r="Q11" t="n">
-        <v>360</v>
+        <v>1395</v>
       </c>
       <c r="R11" t="n">
-        <v>3871</v>
+        <v>2651</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,115 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>바벨피트니스 서대전네거리역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>barbell10@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1411-4881</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대전 중구 중앙로 8 5층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/barbell10</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyzclgu</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>342</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>96</v>
-      </c>
-      <c r="R12" t="n">
-        <v>438</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2046682649</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2046682649</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -628,10 +628,10 @@
         <v>1154</v>
       </c>
       <c r="Q2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R2" t="n">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -657,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>건축자재,용품</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>순전가설산업</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>safesoon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1442-2338</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 대덕구 대전로 1011</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>http://2331.co.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4469</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="n">
-        <v>1080</v>
+        <v>407</v>
       </c>
       <c r="R3" t="n">
-        <v>5549</v>
+        <v>444</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>16022221</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/16022221</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>트레인휘트니스 유성점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>train_fitness1@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6142</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 유성구 온천서로 2 케이티온 유성타워 2층 201호</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/train_fitness1</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuudbce</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>967</v>
+        <v>1270</v>
       </c>
       <c r="Q4" t="n">
-        <v>543</v>
+        <v>204</v>
       </c>
       <c r="R4" t="n">
-        <v>1510</v>
+        <v>1474</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1881350370</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881350370</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>원알엠 PT &amp; 재활트레이닝 관저점</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1rmgym@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1311-1989</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 서구 관저로 25 초이스프라자 5층</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1rmgym/224197109345</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44jzd</t>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>728</v>
+        <v>4469</v>
       </c>
       <c r="Q5" t="n">
-        <v>638</v>
+        <v>1080</v>
       </c>
       <c r="R5" t="n">
-        <v>1366</v>
+        <v>5549</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1117865840</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117865840</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>위온 휘트니스 월평점</t>
+          <t>트레인휘트니스 유성점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>weonfitness1@naver.com</t>
+          <t>train_fitness1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>042-488-1101</t>
+          <t>0507-1343-6142</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 서구 청사로 65 황실코아 B1층</t>
+          <t>대전 유성구 온천서로 2 케이티온 유성타워 2층 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/weonfitness1</t>
+          <t>https://blog.naver.com/train_fitness1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -994,14 +994,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wbsx2z0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>395</v>
+        <v>967</v>
       </c>
       <c r="Q6" t="n">
-        <v>205</v>
+        <v>543</v>
       </c>
       <c r="R6" t="n">
-        <v>600</v>
+        <v>1510</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2031828897</t>
+          <t>1881350370</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031828897</t>
+          <t>https://m.place.naver.com/place/1881350370</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바벨피트니스 둔산탄방점</t>
+          <t>원알엠 PT &amp; 재활트레이닝 관저점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fit34@naver.com</t>
+          <t>1rmgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1334-1836</t>
+          <t>0507-1311-1989</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 220 7층 701,702,703호</t>
+          <t>대전 서구 관저로 25 초이스프라자 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbell_SIX6th/</t>
+          <t>https://blog.naver.com/1rmgym/224197109345</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ychq</t>
+          <t>https://talk.naver.com/ct/w44jzd</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>640</v>
+        <v>730</v>
       </c>
       <c r="Q7" t="n">
-        <v>129</v>
+        <v>638</v>
       </c>
       <c r="R7" t="n">
-        <v>769</v>
+        <v>1368</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1274875802</t>
+          <t>1117865840</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274875802</t>
+          <t>https://m.place.naver.com/place/1117865840</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>위온 휘트니스 월평점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>weonfitness1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>042-488-1101</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
+          <t>대전 서구 청사로 65 황실코아 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jupilates11</t>
+          <t>https://blog.naver.com/weonfitness1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
+          <t>https://talk.naver.com/ct/wbsx2z0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>395</v>
       </c>
       <c r="Q8" t="n">
-        <v>339</v>
+        <v>205</v>
       </c>
       <c r="R8" t="n">
-        <v>455</v>
+        <v>600</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1618277867</t>
+          <t>2031828897</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
+          <t>https://m.place.naver.com/place/2031828897</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포레스트 필라테스 괴정점</t>
+          <t>바벨피트니스 둔산탄방점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>forestgigu@naver.com</t>
+          <t>fit34@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-9684</t>
+          <t>0507-1334-1836</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
+          <t>대전 서구 둔산로 220 7층 701,702,703호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestpila__gj</t>
+          <t>https://www.instagram.com/barbell_SIX6th/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlha8ui</t>
+          <t>https://talk.naver.com/ct/w5ychq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="Q9" t="n">
-        <v>856</v>
+        <v>130</v>
       </c>
       <c r="R9" t="n">
-        <v>1490</v>
+        <v>771</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1359870527</t>
+          <t>1274875802</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359870527</t>
+          <t>https://m.place.naver.com/place/1274875802</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>주 필라테스&amp;요가 관평점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>jugwpy7755@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1399-7758</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3511</v>
+        <v>116</v>
       </c>
       <c r="Q10" t="n">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="R10" t="n">
-        <v>3871</v>
+        <v>455</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>1618277867</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>포레스트 필라테스 괴정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>forestgigu@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1428-9684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://www.instagram.com/forestpila__gj</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/wlha8ui</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1256</v>
+        <v>635</v>
       </c>
       <c r="Q11" t="n">
-        <v>1395</v>
+        <v>857</v>
       </c>
       <c r="R11" t="n">
-        <v>2651</v>
+        <v>1492</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1514,211 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1359870527</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1359870527</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gymforxe_2nd@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1307-9497</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wccep6d</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3513</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>360</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3873</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1868031100</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868031100</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>바벨피트니스 서대전네거리역점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>barbell10@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1411-4881</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대전 중구 중앙로 8 5층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbell10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyzclgu</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>97</v>
+      </c>
+      <c r="R13" t="n">
+        <v>441</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2046682649</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046682649</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,46 +650,46 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>건축자재,용품</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>순전가설산업</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>safesoon@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1442-2338</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 대덕구 대전로 1011</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://2331.co.kr</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuudbce</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +719,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>37</v>
+        <v>1270</v>
       </c>
       <c r="Q3" t="n">
-        <v>407</v>
+        <v>204</v>
       </c>
       <c r="R3" t="n">
-        <v>444</v>
+        <v>1474</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16022221</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16022221</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>모던 휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>mr2416_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1375-2416</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 중구 목중로 22 2층,3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://blog.naver.com/mr2416_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/wqu7g29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1270</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>1474</v>
+        <v>242</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1966964430</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1966964430</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Q7" t="n">
         <v>638</v>
       </c>
       <c r="R7" t="n">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>포레스트 필라테스 괴정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>forestgigu@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>0507-1428-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
+          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jupilates11</t>
+          <t>https://www.instagram.com/forestpila__gj</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
+          <t>https://talk.naver.com/ct/wlha8ui</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>116</v>
+        <v>635</v>
       </c>
       <c r="Q10" t="n">
-        <v>339</v>
+        <v>857</v>
       </c>
       <c r="R10" t="n">
-        <v>455</v>
+        <v>1492</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1618277867</t>
+          <t>1359870527</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
+          <t>https://m.place.naver.com/place/1359870527</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포레스트 필라테스 괴정점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>forestgigu@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1428-9684</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 갈마로 255 6층 포레스트기구필라테스 괴정점</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestpila__gj</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlha8ui</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>635</v>
+        <v>3513</v>
       </c>
       <c r="Q11" t="n">
-        <v>857</v>
+        <v>360</v>
       </c>
       <c r="R11" t="n">
-        <v>1492</v>
+        <v>3873</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,213 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1359870527</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359870527</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gymforxe_2nd@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1307-9497</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3513</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>360</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3873</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1868031100</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>바벨피트니스 서대전네거리역점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>barbell10@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1411-4881</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대전 중구 중앙로 8 5층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/barbell10</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyzclgu</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>344</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>97</v>
-      </c>
-      <c r="R13" t="n">
-        <v>441</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2046682649</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2046682649</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_PT.xlsx
+++ b/naver-place-crawler/results_health/대전_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>barbellf07@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1466-6683</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 중구 중앙로164번길 22-12 3층</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbellf07</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uuci</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1154</v>
+        <v>1256</v>
       </c>
       <c r="Q2" t="n">
-        <v>200</v>
+        <v>1395</v>
       </c>
       <c r="R2" t="n">
-        <v>1354</v>
+        <v>2651</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1141342986</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141342986</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>뉴로트레이닝 &amp; 근골격계 재활 PT 더 조아짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>sobia9991@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1477-7943</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 서구 둔산로31번길 77 사리원 5층 모토 컨트롤 뉴로트레이닝 둔산동 더 조아짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://www.instagram.com/ptzoa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1270</v>
+        <v>168</v>
       </c>
       <c r="Q3" t="n">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="R3" t="n">
-        <v>1474</v>
+        <v>477</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1131791300</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1131791300</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>모던 휘트니스</t>
+          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mr2416_@naver.com</t>
+          <t>barbellf07@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-2416</t>
+          <t>0507-1466-6683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 중구 목중로 22 2층,3층</t>
+          <t>대전 중구 중앙로164번길 22-12 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mr2416_</t>
+          <t>https://blog.naver.com/barbellf07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqu7g29</t>
+          <t>https://talk.naver.com/ct/w5uuci</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>61</v>
+        <v>1154</v>
       </c>
       <c r="Q4" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="R4" t="n">
-        <v>242</v>
+        <v>1354</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1966964430</t>
+          <t>1141342986</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966964430</t>
+          <t>https://m.place.naver.com/place/1141342986</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4469</v>
+        <v>4470</v>
       </c>
       <c r="Q5" t="n">
         <v>1080</v>
       </c>
       <c r="R5" t="n">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1114,10 +1110,10 @@
         <v>731</v>
       </c>
       <c r="Q7" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R7" t="n">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1437,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3513</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>360</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>3873</v>
+        <v>169</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1514,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>16151158</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/16151158</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>바벨피트니스 서대전네거리역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>barbell10@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1411-4881</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 중구 중앙로 8 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbell10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyzclgu</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>97</v>
+      </c>
+      <c r="R12" t="n">
+        <v>441</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2046682649</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046682649</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
